--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -31,22 +31,22 @@
     <t>Unique bond count</t>
   </si>
   <si>
+    <t>CoIn2</t>
+  </si>
+  <si>
     <t>CoIn3</t>
   </si>
   <si>
-    <t>CoIn2</t>
+    <t>Mg2Cu</t>
   </si>
   <si>
     <t>U3Si2</t>
   </si>
   <si>
+    <t>RuIn3</t>
+  </si>
+  <si>
     <t>IrIn3</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -486,7 +486,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -512,7 +512,7 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -520,7 +520,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -614,7 +614,7 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
   <si>
     <t>Formula</t>
   </si>
@@ -28,7 +28,13 @@
     <t>Bond count</t>
   </si>
   <si>
-    <t>Unique bond count</t>
+    <t>No duplicate bond count</t>
+  </si>
+  <si>
+    <t>Average bond length</t>
+  </si>
+  <si>
+    <t>Std dev</t>
   </si>
   <si>
     <t>CoIn2</t>
@@ -40,13 +46,13 @@
     <t>Mg2Cu</t>
   </si>
   <si>
+    <t>IrIn3</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
+  </si>
+  <si>
     <t>U3Si2</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -413,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,33 +438,45 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -466,101 +484,137 @@
       <c r="E3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>2.708</v>
+      </c>
+      <c r="G3">
+        <v>0.037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>2.608</v>
+      </c>
+      <c r="G7">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -568,72 +622,102 @@
       <c r="E11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>2.62</v>
+      </c>
+      <c r="G11">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>2.597</v>
+      </c>
+      <c r="G15">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>0</v>
       </c>
     </row>

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -37,22 +37,22 @@
     <t>Std dev</t>
   </si>
   <si>
+    <t>CoIn3</t>
+  </si>
+  <si>
     <t>CoIn2</t>
   </si>
   <si>
-    <t>CoIn3</t>
+    <t>IrIn3</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
   </si>
   <si>
     <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -479,16 +479,16 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2.708</v>
+        <v>2.608</v>
       </c>
       <c r="G3">
-        <v>0.037</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -516,7 +516,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -548,21 +548,21 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>2.608</v>
+        <v>2.62</v>
       </c>
       <c r="G7">
-        <v>0.011</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -608,7 +608,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -623,15 +623,15 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>2.62</v>
+        <v>2.597</v>
       </c>
       <c r="G11">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>2.597</v>
+        <v>2.708</v>
       </c>
       <c r="G15">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -37,22 +37,22 @@
     <t>Std dev</t>
   </si>
   <si>
+    <t>CoIn2</t>
+  </si>
+  <si>
     <t>CoIn3</t>
   </si>
   <si>
-    <t>CoIn2</t>
+    <t>Mg2Cu</t>
   </si>
   <si>
     <t>IrIn3</t>
   </si>
   <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
     <t>RuIn3</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -479,16 +479,16 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2.608</v>
+        <v>2.708</v>
       </c>
       <c r="G3">
-        <v>0.011</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -516,7 +516,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -548,21 +548,21 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>2.62</v>
+        <v>2.608</v>
       </c>
       <c r="G7">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -608,7 +608,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>2.708</v>
+        <v>2.62</v>
       </c>
       <c r="G15">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -37,22 +37,22 @@
     <t>Std dev</t>
   </si>
   <si>
+    <t>CoIn3</t>
+  </si>
+  <si>
     <t>CoIn2</t>
   </si>
   <si>
-    <t>CoIn3</t>
+    <t>IrIn3</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
+    <t>RuIn3</t>
   </si>
   <si>
     <t>Mg2Cu</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
   </si>
   <si>
     <t>Co-Co</t>
@@ -479,16 +479,16 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2.708</v>
+        <v>2.608</v>
       </c>
       <c r="G3">
-        <v>0.037</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -516,7 +516,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -548,21 +548,21 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>2.608</v>
+        <v>2.597</v>
       </c>
       <c r="G7">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -608,7 +608,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -623,15 +623,15 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>2.597</v>
+        <v>2.62</v>
       </c>
       <c r="G11">
-        <v>0.006</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>2.62</v>
+        <v>2.708</v>
       </c>
       <c r="G15">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="16" spans="1:7">

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -43,10 +43,10 @@
     <t>CoIn2</t>
   </si>
   <si>
+    <t>U3Si2</t>
+  </si>
+  <si>
     <t>IrIn3</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
   </si>
   <si>
     <t>RuIn3</t>
@@ -479,16 +479,16 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2.608</v>
+        <v>2.597</v>
       </c>
       <c r="G3">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -548,16 +548,16 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>2.597</v>
+        <v>2.608</v>
       </c>
       <c r="G7">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/system_analysis_structures.xlsx
+++ b/system_analysis_structures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="36">
   <si>
     <t>Formula</t>
   </si>
@@ -37,28 +37,88 @@
     <t>Std dev</t>
   </si>
   <si>
-    <t>CoIn3</t>
-  </si>
-  <si>
-    <t>CoIn2</t>
-  </si>
-  <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
-    <t>IrIn3</t>
-  </si>
-  <si>
-    <t>RuIn3</t>
-  </si>
-  <si>
-    <t>Mg2Cu</t>
+    <t>Er3Co2In4</t>
+  </si>
+  <si>
+    <t>ErCoIn5</t>
+  </si>
+  <si>
+    <t>ErCo4In</t>
+  </si>
+  <si>
+    <t>ErCo2.68In0.32</t>
+  </si>
+  <si>
+    <t>Er3Co1.87In4</t>
+  </si>
+  <si>
+    <t>Er11Co4In9</t>
+  </si>
+  <si>
+    <t>Er2CoIn8</t>
+  </si>
+  <si>
+    <t>Er6Co2.19In0.81</t>
+  </si>
+  <si>
+    <t>Er8CoIn3</t>
+  </si>
+  <si>
+    <t>Er10Co9In20</t>
+  </si>
+  <si>
+    <t>Er14Co2In3</t>
+  </si>
+  <si>
+    <t>Er14Co3In3</t>
+  </si>
+  <si>
+    <t>Lu3Co2In4</t>
+  </si>
+  <si>
+    <t>HoCoGa5</t>
+  </si>
+  <si>
+    <t>MgCu4Sn</t>
+  </si>
+  <si>
+    <t>PuNi3</t>
+  </si>
+  <si>
+    <t>Nd11Pd4In9</t>
+  </si>
+  <si>
+    <t>Ho2CoGa8</t>
+  </si>
+  <si>
+    <t>Ho6Co2Ga</t>
+  </si>
+  <si>
+    <t>Pr8CoGa3</t>
+  </si>
+  <si>
+    <t>Ho10Ni9In20</t>
+  </si>
+  <si>
+    <t>Lu14Co2In3</t>
+  </si>
+  <si>
+    <t>Gd14Co3In2.7</t>
   </si>
   <si>
     <t>Co-Co</t>
   </si>
   <si>
     <t>Co-In</t>
+  </si>
+  <si>
+    <t>Er-Co</t>
+  </si>
+  <si>
+    <t>Er-Er</t>
+  </si>
+  <si>
+    <t>Er-In</t>
   </si>
   <si>
     <t>In-In</t>
@@ -419,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,10 +510,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -473,22 +533,22 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>2.597</v>
+        <v>2.705</v>
       </c>
       <c r="G3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -496,21 +556,44 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
     </row>
@@ -519,10 +602,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -542,102 +625,102 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>2.948</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>2.608</v>
-      </c>
-      <c r="G7">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2.569</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -650,6 +733,29 @@
       </c>
       <c r="G12">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>3.079</v>
+      </c>
+      <c r="G13">
+        <v>0.17</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -657,68 +763,1402 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>3.199</v>
       </c>
       <c r="G14">
         <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>2.708</v>
-      </c>
-      <c r="G15">
-        <v>0.037</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2.492</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>2.922</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>2.922</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2.471</v>
+      </c>
+      <c r="G23">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>2.471</v>
+      </c>
+      <c r="G24">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>2.864</v>
+      </c>
+      <c r="G25">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>2.864</v>
+      </c>
+      <c r="G27">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>2.471</v>
+      </c>
+      <c r="G28">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>2.687</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>2.799</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>2.949</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>2.984</v>
+      </c>
+      <c r="G38">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>2.831</v>
+      </c>
+      <c r="G39">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>3.179</v>
+      </c>
+      <c r="G41">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>2.947</v>
+      </c>
+      <c r="G42">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>2.687</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>3.222</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>3.157</v>
+      </c>
+      <c r="G49">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>2.297</v>
+      </c>
+      <c r="G51">
+        <v>0.093</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>2.834</v>
+      </c>
+      <c r="G53">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>3.124</v>
+      </c>
+      <c r="G55">
+        <v>0.228</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60">
+        <v>6</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>2.807</v>
+      </c>
+      <c r="G60">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>3.179</v>
+      </c>
+      <c r="G62">
+        <v>0.202</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66">
+        <v>12</v>
+      </c>
+      <c r="E66">
+        <v>3</v>
+      </c>
+      <c r="F66">
+        <v>2.685</v>
+      </c>
+      <c r="G66">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67">
         <v>8</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>2.962</v>
+      </c>
+      <c r="G67">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>2.975</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>2.72</v>
+      </c>
+      <c r="G74">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>3.203</v>
+      </c>
+      <c r="G76">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>2.999</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>2.964</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>2.964</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>2.762</v>
+      </c>
+      <c r="G81">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>3.183</v>
+      </c>
+      <c r="G83">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>3.104</v>
+      </c>
+      <c r="G84">
+        <v>0.135</v>
       </c>
     </row>
   </sheetData>
